--- a/plantilla.xlsx
+++ b/plantilla.xlsx
@@ -169,7 +169,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Composición sugerida del portafolio</a:t>
+              <a:t>Cartera asignada</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -234,9 +234,9 @@
             </spPr>
           </dPt>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Datos'!$A$2:$A$4</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -423,6 +423,1115 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cartera de equilibrio</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Datos'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B3BC80"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <strRef>
+              <f>'Datos'!$A$2:$A$4</f>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Datos'!$C$2:$C$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CR" sz="1200" b="1"/>
+              <a:t>Rendimiento de equilibrio</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$E$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$E$2:$E$82</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$F$2:$F$82</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$2</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$2</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$3</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$3</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$4</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$4</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$5</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="12"/>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$5</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$5</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$7</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15875">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$7:$I$9</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$7:$J$9</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$6</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="918042"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$6</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$6</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="501"/>
+        <c:axId val="502"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="501"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.2"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CR" sz="900" b="1"/>
+                  <a:t>Riesgo del portafolio (volatilidad anual)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2B3014"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800"/>
+            </a:pPr>
+            <a:endParaRPr lang="es-CR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="502"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.05"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="502"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D9DCCB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CR" sz="900" b="1"/>
+                  <a:t>Rendimiento esperado anual</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2B3014"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800"/>
+            </a:pPr>
+            <a:endParaRPr lang="es-CR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="501"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:srgbClr val="D9DCCB"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CR" sz="1200" b="1"/>
+              <a:t>Posición: tolerancia y apetito</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$A$9</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="6E7356"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$B$9</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$C$9</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$A$10</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="6E7356"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$B$10</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$C$10</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$A$11</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="6E7356"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$B$11</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$C$11</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$A$12</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="6E7356"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$B$12</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$C$12</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$A$7</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="10"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$B$7</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$C$7</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="501"/>
+        <c:axId val="502"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="501"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D9DCCB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CR" sz="900" b="1"/>
+                  <a:t>Tolerancia al riesgo</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2B3014"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800"/>
+            </a:pPr>
+            <a:endParaRPr lang="es-CR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="502"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="502"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D9DCCB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CR" sz="900" b="1"/>
+                  <a:t>Apetito de riesgo</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2B3014"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="800"/>
+            </a:pPr>
+            <a:endParaRPr lang="es-CR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="501"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:srgbClr val="D9DCCB"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -442,6 +1551,72 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3420000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
